--- a/tests/TC-02/results/teacher_timetables_even.xlsx
+++ b/tests/TC-02/results/teacher_timetables_even.xlsx
@@ -56,14 +56,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BBDEFB"/>
-        <bgColor rgb="00BBDEFB"/>
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00BBDEFB"/>
+        <bgColor rgb="00BBDEFB"/>
       </patternFill>
     </fill>
   </fills>
@@ -651,18 +651,8 @@
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr"/>
       <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 103</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 103</t>
-        </is>
-      </c>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="4" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr"/>
       <c r="N4" s="4" t="inlineStr"/>
@@ -694,9 +684,24 @@
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 101</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 101</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 101</t>
+        </is>
+      </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
@@ -712,38 +717,33 @@
       <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 102</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 102</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 102</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 102</t>
-        </is>
-      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr"/>
       <c r="N6" s="4" t="inlineStr"/>
       <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 101</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 101</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 101</t>
+        </is>
+      </c>
       <c r="S6" s="4" t="inlineStr"/>
       <c r="T6" s="4" t="inlineStr"/>
       <c r="U6" s="4" t="inlineStr"/>
@@ -757,36 +757,21 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 102</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 102</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 102</t>
-        </is>
-      </c>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 102</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
@@ -990,18 +975,8 @@
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr"/>
       <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="4" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr"/>
       <c r="N4" s="4" t="inlineStr"/>
@@ -1033,9 +1008,24 @@
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
@@ -1051,38 +1041,33 @@
       <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 103</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 103</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 103</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 103</t>
-        </is>
-      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr"/>
       <c r="N6" s="4" t="inlineStr"/>
       <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
       <c r="S6" s="4" t="inlineStr"/>
       <c r="T6" s="4" t="inlineStr"/>
       <c r="U6" s="4" t="inlineStr"/>
@@ -1096,36 +1081,21 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 103</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 103</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 103</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 103</t>
-        </is>
-      </c>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 103</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
